--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104239</v>
+        <v>104240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104240</v>
+        <v>104245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104245</v>
+        <v>104249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104249</v>
+        <v>104251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104251</v>
+        <v>104261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734725</v>
       </c>
       <c r="B2" t="n">
-        <v>104261</v>
+        <v>104265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129734802</v>
       </c>
       <c r="B3" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51933-2025 artfynd.xlsx
+++ b/artfynd/A 51933-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129734725</v>
+        <v>129734802</v>
       </c>
       <c r="B2" t="n">
-        <v>104301</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -756,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,16 +773,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ett område med blandad skog i viss varierande ålder. Stor förekomst av död ved i olika netbrytningstadier, huvudsakligen av gran och björk.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -799,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129734802</v>
+        <v>129734725</v>
       </c>
       <c r="B3" t="n">
-        <v>98864</v>
+        <v>104627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,26 +800,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +829,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -880,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +887,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ett område med blandad skog i viss varierande ålder. Stor förekomst av död ved i olika netbrytningstadier, huvudsakligen av gran och björk.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
